--- a/Results/Sit_To_Stand/Normal/Results_Comparison_Fixed_PCA95_Sit_To_Stand.xlsx
+++ b/Results/Sit_To_Stand/Normal/Results_Comparison_Fixed_PCA95_Sit_To_Stand.xlsx
@@ -469,19 +469,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.53333333333333</v>
+        <v>79.73333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>78.26825396825397</v>
+        <v>83.01851851851852</v>
       </c>
       <c r="D2" t="n">
-        <v>76.53333333333333</v>
+        <v>79.73333333333335</v>
       </c>
       <c r="E2" t="n">
-        <v>88.26666666666667</v>
+        <v>89.86666666666666</v>
       </c>
       <c r="F2" t="n">
-        <v>75.77602397602396</v>
+        <v>79.12062012062012</v>
       </c>
     </row>
     <row r="3">
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.59999999999999</v>
+        <v>68.26666666666665</v>
       </c>
       <c r="C3" t="n">
-        <v>74.67248677248678</v>
+        <v>70.85396825396825</v>
       </c>
       <c r="D3" t="n">
-        <v>73.59999999999999</v>
+        <v>68.26666666666665</v>
       </c>
       <c r="E3" t="n">
-        <v>86.8</v>
+        <v>84.13333333333334</v>
       </c>
       <c r="F3" t="n">
-        <v>72.65315425315424</v>
+        <v>67.5137159137159</v>
       </c>
     </row>
     <row r="4">
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.06666666666666</v>
+        <v>67.46666666666667</v>
       </c>
       <c r="C4" t="n">
-        <v>66.96243386243385</v>
+        <v>71.67378547378547</v>
       </c>
       <c r="D4" t="n">
-        <v>65.06666666666666</v>
+        <v>67.46666666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>82.53333333333335</v>
+        <v>83.73333333333332</v>
       </c>
       <c r="F4" t="n">
-        <v>62.97225737225738</v>
+        <v>65.20371850371851</v>
       </c>
     </row>
   </sheetData>
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>76.53333333333333</v>
+        <v>79.73333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>78.26825396825397</v>
+        <v>83.01851851851852</v>
       </c>
       <c r="E2" t="n">
-        <v>76.53333333333333</v>
+        <v>79.73333333333335</v>
       </c>
       <c r="F2" t="n">
-        <v>88.26666666666667</v>
+        <v>89.86666666666666</v>
       </c>
       <c r="G2" t="n">
-        <v>75.77602397602396</v>
+        <v>79.12062012062012</v>
       </c>
     </row>
     <row r="3">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73.59999999999999</v>
+        <v>68.26666666666665</v>
       </c>
       <c r="D3" t="n">
-        <v>74.67248677248678</v>
+        <v>70.85396825396825</v>
       </c>
       <c r="E3" t="n">
-        <v>73.59999999999999</v>
+        <v>68.26666666666665</v>
       </c>
       <c r="F3" t="n">
-        <v>86.8</v>
+        <v>84.13333333333334</v>
       </c>
       <c r="G3" t="n">
-        <v>72.65315425315424</v>
+        <v>67.5137159137159</v>
       </c>
     </row>
     <row r="4">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>65.06666666666666</v>
+        <v>67.46666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>66.96243386243385</v>
+        <v>71.67378547378547</v>
       </c>
       <c r="E4" t="n">
-        <v>65.06666666666666</v>
+        <v>67.46666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>82.53333333333335</v>
+        <v>83.73333333333332</v>
       </c>
       <c r="G4" t="n">
-        <v>62.97225737225738</v>
+        <v>65.20371850371851</v>
       </c>
     </row>
   </sheetData>
@@ -715,19 +715,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="D2" t="n">
-        <v>37.14285714285715</v>
+        <v>54.92063492063492</v>
       </c>
       <c r="E2" t="n">
-        <v>46.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>73.33333333333334</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>41.11111111111111</v>
+        <v>56.11111111111111</v>
       </c>
     </row>
     <row r="3">
@@ -765,19 +765,19 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D4" t="n">
-        <v>74.07407407407408</v>
+        <v>79.16666666666666</v>
       </c>
       <c r="E4" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F4" t="n">
-        <v>83.33333333333334</v>
+        <v>86.66666666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>65.47619047619048</v>
+        <v>72.86324786324786</v>
       </c>
     </row>
     <row r="5">
@@ -790,19 +790,19 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>83.33333333333334</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>79.54545454545455</v>
+        <v>86.5993265993266</v>
       </c>
     </row>
     <row r="6">
@@ -815,19 +815,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>53.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>51.85185185185185</v>
+        <v>71.85185185185186</v>
       </c>
       <c r="E6" t="n">
-        <v>53.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>76.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="G6" t="n">
-        <v>48.14814814814815</v>
+        <v>54.92063492063492</v>
       </c>
     </row>
     <row r="7">
@@ -840,19 +840,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D7" t="n">
-        <v>49.44444444444444</v>
+        <v>64.44444444444444</v>
       </c>
       <c r="E7" t="n">
-        <v>53.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F7" t="n">
-        <v>76.66666666666666</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>51.04377104377105</v>
+        <v>65.11784511784512</v>
       </c>
     </row>
     <row r="8">
@@ -893,7 +893,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="D9" t="n">
-        <v>74.07407407407408</v>
+        <v>76.85185185185185</v>
       </c>
       <c r="E9" t="n">
         <v>66.66666666666666</v>
@@ -902,7 +902,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>65.47619047619048</v>
+        <v>65.07936507936508</v>
       </c>
     </row>
     <row r="10">
@@ -915,19 +915,19 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>53.33333333333334</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="D10" t="n">
-        <v>61.11111111111111</v>
+        <v>59.59595959595959</v>
       </c>
       <c r="E10" t="n">
-        <v>53.33333333333334</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="F10" t="n">
-        <v>76.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>49.60317460317461</v>
+        <v>40.27777777777777</v>
       </c>
     </row>
     <row r="11">
@@ -943,7 +943,7 @@
         <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>60</v>
+        <v>58.73015873015873</v>
       </c>
       <c r="E11" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         <v>80</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>56.49350649350649</v>
       </c>
     </row>
     <row r="12">
@@ -965,19 +965,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>73.33333333333333</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>73.80952380952381</v>
+        <v>83.80952380952381</v>
       </c>
       <c r="E12" t="n">
-        <v>73.33333333333334</v>
+        <v>80</v>
       </c>
       <c r="F12" t="n">
-        <v>86.66666666666667</v>
+        <v>90</v>
       </c>
       <c r="G12" t="n">
-        <v>72.22222222222221</v>
+        <v>79.44444444444444</v>
       </c>
     </row>
     <row r="13">
@@ -1015,19 +1015,19 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>73.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D14" t="n">
-        <v>72.69841269841271</v>
+        <v>68.05555555555554</v>
       </c>
       <c r="E14" t="n">
-        <v>73.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F14" t="n">
-        <v>86.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G14" t="n">
-        <v>71.11111111111111</v>
+        <v>64.52991452991452</v>
       </c>
     </row>
     <row r="15">
@@ -1040,19 +1040,19 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>79.44444444444444</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>79.1919191919192</v>
+        <v>72.22222222222221</v>
       </c>
     </row>
     <row r="16">
@@ -1065,19 +1065,19 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D16" t="n">
-        <v>57.50000000000001</v>
+        <v>68.05555555555554</v>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F16" t="n">
-        <v>80.00000000000001</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>55.16483516483516</v>
+        <v>64.52991452991452</v>
       </c>
     </row>
     <row r="17">
@@ -1115,19 +1115,19 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D18" t="n">
-        <v>55.55555555555555</v>
+        <v>68.05555555555554</v>
       </c>
       <c r="E18" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F18" t="n">
-        <v>80.00000000000001</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>56.81818181818182</v>
+        <v>64.52991452991452</v>
       </c>
     </row>
     <row r="19">
@@ -1165,19 +1165,19 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>60</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D20" t="n">
-        <v>73.14814814814815</v>
+        <v>85.18518518518518</v>
       </c>
       <c r="E20" t="n">
-        <v>60</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>60.31746031746032</v>
+        <v>73.80952380952381</v>
       </c>
     </row>
     <row r="21">
@@ -1190,19 +1190,19 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>53.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="D21" t="n">
-        <v>48.80952380952381</v>
+        <v>54.92063492063492</v>
       </c>
       <c r="E21" t="n">
-        <v>53.33333333333334</v>
+        <v>60</v>
       </c>
       <c r="F21" t="n">
-        <v>76.66666666666666</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>56.11111111111111</v>
       </c>
     </row>
     <row r="22">
@@ -1215,19 +1215,19 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D22" t="n">
-        <v>73.88888888888889</v>
+        <v>88.8888888888889</v>
       </c>
       <c r="E22" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G22" t="n">
-        <v>73.13131313131315</v>
+        <v>85.60606060606061</v>
       </c>
     </row>
     <row r="23">
@@ -1243,7 +1243,7 @@
         <v>66.66666666666666</v>
       </c>
       <c r="D23" t="n">
-        <v>64.44444444444444</v>
+        <v>65.47619047619048</v>
       </c>
       <c r="E23" t="n">
         <v>66.66666666666666</v>
@@ -1252,7 +1252,7 @@
         <v>83.33333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>65.11784511784512</v>
+        <v>64.81481481481482</v>
       </c>
     </row>
     <row r="24">
@@ -1265,19 +1265,19 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>73.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D24" t="n">
-        <v>79.16666666666666</v>
+        <v>76.85185185185185</v>
       </c>
       <c r="E24" t="n">
-        <v>73.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F24" t="n">
-        <v>86.66666666666666</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G24" t="n">
-        <v>72.86324786324786</v>
+        <v>65.07936507936508</v>
       </c>
     </row>
     <row r="25">
@@ -1290,19 +1290,19 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D25" t="n">
-        <v>60.18518518518518</v>
+        <v>55.55555555555555</v>
       </c>
       <c r="E25" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F25" t="n">
-        <v>80</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G25" t="n">
-        <v>55.55555555555555</v>
+        <v>48.41269841269841</v>
       </c>
     </row>
     <row r="26">
@@ -1315,19 +1315,19 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D26" t="n">
-        <v>59.72222222222222</v>
+        <v>65.18518518518518</v>
       </c>
       <c r="E26" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F26" t="n">
-        <v>80.00000000000001</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G26" t="n">
-        <v>57.12250712250713</v>
+        <v>48.25396825396826</v>
       </c>
     </row>
     <row r="27">
@@ -1340,19 +1340,19 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D27" t="n">
-        <v>72.22222222222221</v>
+        <v>85.18518518518518</v>
       </c>
       <c r="E27" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F27" t="n">
-        <v>83.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>66.8091168091168</v>
+        <v>72.48677248677248</v>
       </c>
     </row>
     <row r="28">
@@ -1368,16 +1368,16 @@
         <v>80</v>
       </c>
       <c r="D28" t="n">
-        <v>83.33333333333334</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>80</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="F28" t="n">
         <v>90</v>
       </c>
       <c r="G28" t="n">
-        <v>79.54545454545455</v>
+        <v>80.00000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1390,19 +1390,19 @@
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D29" t="n">
-        <v>90.47619047619048</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E29" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>87.03703703703704</v>
+        <v>93.26599326599326</v>
       </c>
     </row>
     <row r="30">
@@ -1440,19 +1440,19 @@
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>73.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D31" t="n">
-        <v>73.88888888888889</v>
+        <v>67.93650793650792</v>
       </c>
       <c r="E31" t="n">
-        <v>73.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F31" t="n">
-        <v>86.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G31" t="n">
-        <v>73.13131313131315</v>
+        <v>65.55555555555556</v>
       </c>
     </row>
     <row r="32">
@@ -1465,19 +1465,19 @@
         <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D32" t="n">
-        <v>66.66666666666666</v>
+        <v>80.15873015873015</v>
       </c>
       <c r="E32" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F32" t="n">
-        <v>83.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>65.15151515151516</v>
+        <v>71.57287157287158</v>
       </c>
     </row>
     <row r="33">
@@ -1490,19 +1490,19 @@
         <v>7</v>
       </c>
       <c r="C33" t="n">
-        <v>80</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D33" t="n">
-        <v>83.33333333333334</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F33" t="n">
-        <v>90</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G33" t="n">
-        <v>79.54545454545455</v>
+        <v>93.26599326599326</v>
       </c>
     </row>
     <row r="34">
@@ -1540,19 +1540,19 @@
         <v>9</v>
       </c>
       <c r="C35" t="n">
-        <v>86.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="D35" t="n">
-        <v>88.8888888888889</v>
+        <v>83.80952380952381</v>
       </c>
       <c r="E35" t="n">
-        <v>86.66666666666667</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>93.33333333333333</v>
+        <v>90</v>
       </c>
       <c r="G35" t="n">
-        <v>85.60606060606061</v>
+        <v>79.44444444444446</v>
       </c>
     </row>
     <row r="36">
@@ -1565,19 +1565,19 @@
         <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D36" t="n">
-        <v>63.33333333333333</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F36" t="n">
-        <v>80</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G36" t="n">
-        <v>61.14478114478113</v>
+        <v>53.8961038961039</v>
       </c>
     </row>
     <row r="37">
@@ -1590,19 +1590,19 @@
         <v>11</v>
       </c>
       <c r="C37" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="D37" t="n">
-        <v>86.66666666666667</v>
+        <v>94.44444444444446</v>
       </c>
       <c r="E37" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="F37" t="n">
-        <v>93.33333333333333</v>
+        <v>96.66666666666667</v>
       </c>
       <c r="G37" t="n">
-        <v>86.66666666666667</v>
+        <v>93.26599326599326</v>
       </c>
     </row>
     <row r="38">
@@ -1618,16 +1618,16 @@
         <v>60</v>
       </c>
       <c r="D38" t="n">
-        <v>61.26984126984127</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="E38" t="n">
         <v>60</v>
       </c>
       <c r="F38" t="n">
-        <v>80.00000000000001</v>
+        <v>80</v>
       </c>
       <c r="G38" t="n">
-        <v>58.88888888888889</v>
+        <v>59.4017094017094</v>
       </c>
     </row>
     <row r="39">
@@ -1643,7 +1643,7 @@
         <v>80</v>
       </c>
       <c r="D39" t="n">
-        <v>80.55555555555554</v>
+        <v>87.5</v>
       </c>
       <c r="E39" t="n">
         <v>80</v>
@@ -1652,7 +1652,7 @@
         <v>90</v>
       </c>
       <c r="G39" t="n">
-        <v>79.79797979797981</v>
+        <v>78.02197802197803</v>
       </c>
     </row>
     <row r="40">
@@ -1690,19 +1690,19 @@
         <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>80</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D41" t="n">
-        <v>82.14285714285715</v>
+        <v>87.77777777777777</v>
       </c>
       <c r="E41" t="n">
-        <v>80</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>90</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G41" t="n">
-        <v>79.62962962962963</v>
+        <v>86.5993265993266</v>
       </c>
     </row>
     <row r="42">
@@ -1715,19 +1715,19 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D42" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="E42" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F42" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G42" t="n">
-        <v>78.02197802197803</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -1765,19 +1765,19 @@
         <v>18</v>
       </c>
       <c r="C44" t="n">
-        <v>73.33333333333333</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D44" t="n">
-        <v>79.36507936507937</v>
+        <v>74.60317460317461</v>
       </c>
       <c r="E44" t="n">
-        <v>73.33333333333334</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F44" t="n">
-        <v>86.66666666666667</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G44" t="n">
-        <v>71.06782106782107</v>
+        <v>65.51226551226551</v>
       </c>
     </row>
     <row r="45">
@@ -1790,19 +1790,19 @@
         <v>19</v>
       </c>
       <c r="C45" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D45" t="n">
-        <v>73.33333333333334</v>
+        <v>90.47619047619048</v>
       </c>
       <c r="E45" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F45" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>73.33333333333334</v>
+        <v>87.03703703703704</v>
       </c>
     </row>
     <row r="46">
@@ -1818,7 +1818,7 @@
         <v>73.33333333333333</v>
       </c>
       <c r="D46" t="n">
-        <v>72.22222222222221</v>
+        <v>72.69841269841271</v>
       </c>
       <c r="E46" t="n">
         <v>73.33333333333334</v>
@@ -1827,7 +1827,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="G46" t="n">
-        <v>71.2121212121212</v>
+        <v>71.11111111111113</v>
       </c>
     </row>
     <row r="47">
@@ -1843,7 +1843,7 @@
         <v>80</v>
       </c>
       <c r="D47" t="n">
-        <v>82.22222222222223</v>
+        <v>87.5</v>
       </c>
       <c r="E47" t="n">
         <v>80.00000000000001</v>
@@ -1852,7 +1852,7 @@
         <v>90</v>
       </c>
       <c r="G47" t="n">
-        <v>80.53872053872054</v>
+        <v>80.27065527065527</v>
       </c>
     </row>
     <row r="48">
@@ -1868,16 +1868,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>83.33333333333334</v>
+        <v>87.5</v>
       </c>
       <c r="E48" t="n">
-        <v>80</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="F48" t="n">
         <v>90</v>
       </c>
       <c r="G48" t="n">
-        <v>79.54545454545455</v>
+        <v>80.27065527065527</v>
       </c>
     </row>
     <row r="49">
@@ -1915,19 +1915,19 @@
         <v>24</v>
       </c>
       <c r="C50" t="n">
-        <v>73.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="D50" t="n">
-        <v>72.69841269841271</v>
+        <v>88.8888888888889</v>
       </c>
       <c r="E50" t="n">
-        <v>73.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="F50" t="n">
-        <v>86.66666666666667</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>71.11111111111111</v>
+        <v>85.60606060606061</v>
       </c>
     </row>
     <row r="51">
@@ -1940,19 +1940,19 @@
         <v>25</v>
       </c>
       <c r="C51" t="n">
-        <v>60</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D51" t="n">
-        <v>57.14285714285715</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="E51" t="n">
-        <v>60</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F51" t="n">
-        <v>80.00000000000001</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G51" t="n">
-        <v>57.4074074074074</v>
+        <v>72.22222222222221</v>
       </c>
     </row>
     <row r="52">
@@ -1990,19 +1990,19 @@
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>80</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D53" t="n">
-        <v>83.33333333333334</v>
+        <v>73.88888888888889</v>
       </c>
       <c r="E53" t="n">
-        <v>80</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F53" t="n">
-        <v>90</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G53" t="n">
-        <v>79.54545454545455</v>
+        <v>73.13131313131315</v>
       </c>
     </row>
     <row r="54">
@@ -2015,19 +2015,19 @@
         <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>86.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="D54" t="n">
-        <v>87.77777777777777</v>
+        <v>79.44444444444444</v>
       </c>
       <c r="E54" t="n">
-        <v>86.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="F54" t="n">
-        <v>93.33333333333333</v>
+        <v>90</v>
       </c>
       <c r="G54" t="n">
-        <v>86.5993265993266</v>
+        <v>79.1919191919192</v>
       </c>
     </row>
     <row r="55">
@@ -2040,19 +2040,19 @@
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D55" t="n">
-        <v>87.77777777777777</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="E55" t="n">
-        <v>86.66666666666667</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F55" t="n">
-        <v>93.33333333333333</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G55" t="n">
-        <v>86.5993265993266</v>
+        <v>71.2121212121212</v>
       </c>
     </row>
     <row r="56">
@@ -2065,19 +2065,19 @@
         <v>5</v>
       </c>
       <c r="C56" t="n">
-        <v>73.33333333333333</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D56" t="n">
-        <v>79.36507936507937</v>
+        <v>54.99999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>73.33333333333334</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F56" t="n">
-        <v>86.66666666666667</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G56" t="n">
-        <v>71.06782106782107</v>
+        <v>53.73737373737374</v>
       </c>
     </row>
     <row r="57">
@@ -2090,19 +2090,19 @@
         <v>6</v>
       </c>
       <c r="C57" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D57" t="n">
-        <v>57.77777777777779</v>
+        <v>80.55555555555554</v>
       </c>
       <c r="E57" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F57" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G57" t="n">
-        <v>58.45117845117846</v>
+        <v>79.79797979797981</v>
       </c>
     </row>
     <row r="58">
@@ -2115,19 +2115,19 @@
         <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>86.66666666666667</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D58" t="n">
-        <v>87.77777777777777</v>
+        <v>77.77777777777779</v>
       </c>
       <c r="E58" t="n">
-        <v>86.66666666666667</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F58" t="n">
-        <v>93.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G58" t="n">
-        <v>86.5993265993266</v>
+        <v>61.92696192696192</v>
       </c>
     </row>
     <row r="59">
@@ -2140,19 +2140,19 @@
         <v>8</v>
       </c>
       <c r="C59" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D59" t="n">
-        <v>62.96296296296296</v>
+        <v>79.44444444444444</v>
       </c>
       <c r="E59" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F59" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G59" t="n">
-        <v>57.14285714285715</v>
+        <v>79.1919191919192</v>
       </c>
     </row>
     <row r="60">
@@ -2165,19 +2165,19 @@
         <v>9</v>
       </c>
       <c r="C60" t="n">
-        <v>80</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D60" t="n">
-        <v>80.55555555555554</v>
+        <v>68.33333333333333</v>
       </c>
       <c r="E60" t="n">
-        <v>80.00000000000001</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F60" t="n">
-        <v>90</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G60" t="n">
-        <v>79.79797979797979</v>
+        <v>67.07070707070706</v>
       </c>
     </row>
     <row r="61">
@@ -2190,19 +2190,19 @@
         <v>10</v>
       </c>
       <c r="C61" t="n">
-        <v>86.66666666666667</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="D61" t="n">
-        <v>87.77777777777777</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="E61" t="n">
-        <v>86.66666666666667</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="F61" t="n">
-        <v>93.33333333333333</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="G61" t="n">
-        <v>86.5993265993266</v>
+        <v>47.76556776556777</v>
       </c>
     </row>
     <row r="62">
@@ -2215,19 +2215,19 @@
         <v>11</v>
       </c>
       <c r="C62" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="D62" t="n">
+        <v>87.77777777777779</v>
+      </c>
+      <c r="E62" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="F62" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="D62" t="n">
-        <v>94.44444444444446</v>
-      </c>
-      <c r="E62" t="n">
-        <v>93.33333333333333</v>
-      </c>
-      <c r="F62" t="n">
-        <v>96.66666666666667</v>
-      </c>
       <c r="G62" t="n">
-        <v>93.26599326599326</v>
+        <v>86.59932659932662</v>
       </c>
     </row>
     <row r="63">
@@ -2240,19 +2240,19 @@
         <v>12</v>
       </c>
       <c r="C63" t="n">
-        <v>40</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D63" t="n">
-        <v>38.33333333333333</v>
+        <v>56.5079365079365</v>
       </c>
       <c r="E63" t="n">
-        <v>40.00000000000001</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F63" t="n">
-        <v>69.99999999999999</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G63" t="n">
-        <v>38.92255892255892</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="64">
@@ -2265,19 +2265,19 @@
         <v>13</v>
       </c>
       <c r="C64" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D64" t="n">
-        <v>66.66666666666666</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="E64" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F64" t="n">
-        <v>80</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G64" t="n">
-        <v>61.36363636363637</v>
+        <v>66.26984126984127</v>
       </c>
     </row>
     <row r="65">
@@ -2293,7 +2293,7 @@
         <v>73.33333333333333</v>
       </c>
       <c r="D65" t="n">
-        <v>72.77777777777779</v>
+        <v>73.80952380952381</v>
       </c>
       <c r="E65" t="n">
         <v>73.33333333333334</v>
@@ -2302,7 +2302,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="G65" t="n">
-        <v>72.52525252525253</v>
+        <v>72.22222222222221</v>
       </c>
     </row>
     <row r="66">
@@ -2315,19 +2315,19 @@
         <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="D66" t="n">
-        <v>63.49206349206349</v>
+        <v>75.55555555555556</v>
       </c>
       <c r="E66" t="n">
-        <v>66.66666666666666</v>
+        <v>73.33333333333334</v>
       </c>
       <c r="F66" t="n">
-        <v>83.33333333333334</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G66" t="n">
-        <v>62.04906204906204</v>
+        <v>73.87205387205387</v>
       </c>
     </row>
     <row r="67">
@@ -2343,7 +2343,7 @@
         <v>73.33333333333333</v>
       </c>
       <c r="D67" t="n">
-        <v>80.15873015873015</v>
+        <v>74.60317460317461</v>
       </c>
       <c r="E67" t="n">
         <v>73.33333333333334</v>
@@ -2352,7 +2352,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="G67" t="n">
-        <v>71.57287157287158</v>
+        <v>72.22222222222221</v>
       </c>
     </row>
     <row r="68">
@@ -2368,7 +2368,7 @@
         <v>80</v>
       </c>
       <c r="D68" t="n">
-        <v>80.55555555555554</v>
+        <v>79.44444444444446</v>
       </c>
       <c r="E68" t="n">
         <v>80.00000000000001</v>
@@ -2377,7 +2377,7 @@
         <v>90</v>
       </c>
       <c r="G68" t="n">
-        <v>79.79797979797979</v>
+        <v>79.1919191919192</v>
       </c>
     </row>
     <row r="69">
@@ -2390,19 +2390,19 @@
         <v>18</v>
       </c>
       <c r="C69" t="n">
-        <v>66.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="D69" t="n">
-        <v>64.44444444444444</v>
+        <v>61.11111111111111</v>
       </c>
       <c r="E69" t="n">
-        <v>66.66666666666666</v>
+        <v>60.00000000000001</v>
       </c>
       <c r="F69" t="n">
-        <v>83.33333333333334</v>
+        <v>80.00000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>65.11784511784512</v>
+        <v>59.09090909090909</v>
       </c>
     </row>
     <row r="70">
@@ -2415,19 +2415,19 @@
         <v>19</v>
       </c>
       <c r="C70" t="n">
-        <v>86.66666666666667</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D70" t="n">
-        <v>87.77777777777777</v>
+        <v>65.55555555555556</v>
       </c>
       <c r="E70" t="n">
-        <v>86.66666666666667</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F70" t="n">
-        <v>93.33333333333333</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G70" t="n">
-        <v>86.5993265993266</v>
+        <v>65.72390572390573</v>
       </c>
     </row>
     <row r="71">
@@ -2440,19 +2440,19 @@
         <v>20</v>
       </c>
       <c r="C71" t="n">
-        <v>66.66666666666666</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="D71" t="n">
-        <v>64.44444444444444</v>
+        <v>55.83333333333334</v>
       </c>
       <c r="E71" t="n">
-        <v>66.66666666666666</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="F71" t="n">
-        <v>83.33333333333334</v>
+        <v>76.66666666666666</v>
       </c>
       <c r="G71" t="n">
-        <v>65.11784511784512</v>
+        <v>51.57509157509158</v>
       </c>
     </row>
     <row r="72">
@@ -2465,19 +2465,19 @@
         <v>21</v>
       </c>
       <c r="C72" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D72" t="n">
-        <v>61.26984126984127</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="E72" t="n">
-        <v>60</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F72" t="n">
-        <v>80</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G72" t="n">
-        <v>58.88888888888889</v>
+        <v>67.42424242424242</v>
       </c>
     </row>
     <row r="73">
@@ -2493,7 +2493,7 @@
         <v>73.33333333333333</v>
       </c>
       <c r="D73" t="n">
-        <v>73.80952380952381</v>
+        <v>75.55555555555556</v>
       </c>
       <c r="E73" t="n">
         <v>73.33333333333334</v>
@@ -2502,7 +2502,7 @@
         <v>86.66666666666667</v>
       </c>
       <c r="G73" t="n">
-        <v>72.22222222222221</v>
+        <v>73.87205387205387</v>
       </c>
     </row>
     <row r="74">
@@ -2515,19 +2515,19 @@
         <v>23</v>
       </c>
       <c r="C74" t="n">
-        <v>80</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="D74" t="n">
-        <v>79.44444444444444</v>
+        <v>63.49206349206349</v>
       </c>
       <c r="E74" t="n">
-        <v>80</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="F74" t="n">
-        <v>90</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="G74" t="n">
-        <v>79.1919191919192</v>
+        <v>62.04906204906204</v>
       </c>
     </row>
     <row r="75">
@@ -2543,16 +2543,16 @@
         <v>73.33333333333333</v>
       </c>
       <c r="D75" t="n">
-        <v>76.38888888888889</v>
+        <v>80.15873015873015</v>
       </c>
       <c r="E75" t="n">
         <v>73.33333333333334</v>
       </c>
       <c r="F75" t="n">
-        <v>86.66666666666666</v>
+        <v>86.66666666666667</v>
       </c>
       <c r="G75" t="n">
-        <v>71.93732193732193</v>
+        <v>71.57287157287158</v>
       </c>
     </row>
     <row r="76">
@@ -2565,19 +2565,19 @@
         <v>25</v>
       </c>
       <c r="C76" t="n">
-        <v>73.33333333333333</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="D76" t="n">
-        <v>73.80952380952381</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="E76" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="F76" t="n">
         <v>73.33333333333334</v>
       </c>
-      <c r="F76" t="n">
-        <v>86.66666666666667</v>
-      </c>
       <c r="G76" t="n">
-        <v>72.22222222222221</v>
+        <v>46.66666666666666</v>
       </c>
     </row>
   </sheetData>
